--- a/src/examples/ELV/data/ELV_ICE_TCs.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_TCs.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="49">
   <si>
     <t xml:space="preserve">process</t>
   </si>
@@ -285,7 +285,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.83"/>
@@ -476,16 +476,16 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0.95</v>
@@ -505,7 +505,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>0.95</v>
@@ -524,8 +524,8 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>22</v>
+      <c r="D12" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>0.95</v>
@@ -544,8 +544,8 @@
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
+      <c r="D13" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0.95</v>
@@ -556,16 +556,16 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>0.95</v>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.95</v>
@@ -605,28 +605,28 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="E17" s="1" t="n">
         <v>0.95</v>
       </c>
@@ -635,7 +635,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -644,8 +644,8 @@
       <c r="C18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>20</v>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.95</v>
@@ -665,32 +665,32 @@
         <v>13</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F20" s="4" t="n">
+      <c r="E20" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F20" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -705,36 +705,36 @@
         <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="23" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -745,7 +745,7 @@
         <v>15</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>0.95</v>
@@ -756,25 +756,25 @@
     </row>
     <row r="24" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -785,12 +785,12 @@
         <v>16</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F25" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F25" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -804,8 +804,8 @@
       <c r="C26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>32</v>
+      <c r="D26" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0.95</v>
@@ -816,16 +816,16 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0.95</v>
@@ -845,7 +845,7 @@
         <v>21</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>0.95</v>
@@ -865,9 +865,9 @@
         <v>21</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>0.95</v>
       </c>
       <c r="F29" s="1" t="n">
@@ -885,12 +885,12 @@
         <v>21</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F30" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F30" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -905,12 +905,12 @@
         <v>21</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>0.95</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="F31" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -925,7 +925,7 @@
         <v>21</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>0.95</v>
@@ -945,7 +945,7 @@
         <v>21</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>0.95</v>
@@ -965,12 +965,12 @@
         <v>21</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F34" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F34" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -985,12 +985,12 @@
         <v>21</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F35" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F35" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1004,8 +1004,8 @@
       <c r="C36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>44</v>
+      <c r="D36" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>0.95</v>
@@ -1016,16 +1016,16 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>0.95</v>
@@ -1045,7 +1045,7 @@
         <v>20</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>0.95</v>
@@ -1065,12 +1065,12 @@
         <v>20</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F39" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F39" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
         <v>20</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F40" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F40" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1104,13 +1104,33 @@
       <c r="C41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F41" s="1" t="n">
+      <c r="E42" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F42" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>

--- a/src/examples/ELV/data/ELV_ICE_TCs.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_TCs.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$F$31</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$F$32</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="43">
   <si>
     <t xml:space="preserve">process</t>
   </si>
@@ -79,22 +79,25 @@
     <t xml:space="preserve">ALL_rubber</t>
   </si>
   <si>
+    <t xml:space="preserve">dismantling_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_parts</t>
+  </si>
+  <si>
     <t xml:space="preserve">collection_ICE</t>
   </si>
   <si>
     <t xml:space="preserve">none</t>
   </si>
   <si>
-    <t xml:space="preserve">ELV_ICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dismantling_ICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELV_ICE_catconverter</t>
+    <t xml:space="preserve">ELV_ICE_catconv</t>
   </si>
   <si>
     <t xml:space="preserve">ELV_ICE_engtrans</t>
@@ -143,14 +146,21 @@
   </si>
   <si>
     <t xml:space="preserve">Pb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PutOnMarket_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW_ICE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -223,7 +233,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -237,6 +247,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -274,13 +288,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="19.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.47"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -316,8 +330,9 @@
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>0.95</v>
+      <c r="E2" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.567606585410564</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.1</v>
@@ -330,14 +345,15 @@
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>0.95</v>
+      <c r="E3" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.975226841898375</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.1</v>
@@ -350,14 +366,15 @@
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0.95</v>
+      <c r="E4" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.30993887734306</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>0.1</v>
@@ -373,11 +390,12 @@
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0.95</v>
+      <c r="E5" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.917705283563195</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.1</v>
@@ -393,11 +411,12 @@
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0.95</v>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.649191589278656</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>0.1</v>
@@ -405,19 +424,20 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0.95</v>
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.207532443436939</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.1</v>
@@ -425,19 +445,20 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>0.95</v>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.624980256183717</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.1</v>
@@ -445,19 +466,20 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0.95</v>
+      <c r="D9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.975329676638525</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>0.1</v>
@@ -465,19 +487,20 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>0.95</v>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.653767790478176</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>0.1</v>
@@ -485,19 +508,20 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0.95</v>
+      <c r="D11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.702911625671856</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>0.1</v>
@@ -505,19 +529,20 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0.95</v>
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.130352751211588</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>0.1</v>
@@ -525,19 +550,20 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>0.95</v>
+      <c r="E13" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.62146025019331</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>0.1</v>
@@ -545,19 +571,20 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>0.95</v>
+      <c r="E14" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.251647985892237</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>0.1</v>
@@ -568,76 +595,80 @@
         <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.427589867002515</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.994698002424131</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F17" s="1" t="n">
+      <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.563930033264676</v>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0.95</v>
+        <v>26</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.0658305426995954</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0.1</v>
@@ -645,19 +676,20 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>0.95</v>
+      <c r="E19" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.585271010368509</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>0.1</v>
@@ -665,19 +697,20 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>24</v>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>0.95</v>
+        <v>32</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.176428802857364</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>0.1</v>
@@ -685,19 +718,20 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0.95</v>
+        <v>32</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.267785630167501</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>0.1</v>
@@ -705,59 +739,62 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="E22" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.895197364189645</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.215037446114134</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="C24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>0.95</v>
+      <c r="E24" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.737851123088268</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>0.1</v>
@@ -765,39 +802,41 @@
     </row>
     <row r="25" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>0.95</v>
+      <c r="E25" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.516436415646474</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>0.95</v>
+        <v>36</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.226250479775035</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>0.1</v>
@@ -805,19 +844,20 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>0.95</v>
+        <v>20</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.237352695016852</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>0.1</v>
@@ -825,19 +865,20 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>0.95</v>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.666864787859761</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>0.1</v>
@@ -848,16 +889,17 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>0.95</v>
+      <c r="E29" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.0202374707868166</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>0.1</v>
@@ -865,19 +907,20 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>0.95</v>
+      <c r="E30" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.540601229266589</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>0.1</v>
@@ -890,21 +933,63 @@
       <c r="B31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F31" s="2" t="n">
+      <c r="E31" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.203187480975926</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.604443658361369</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F33" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F31"/>
+  <autoFilter ref="A1:F32"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/src/examples/ELV/data/ELV_ICE_TCs.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_TCs.xlsx
@@ -331,8 +331,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.567606585410564</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.1</v>
@@ -352,8 +351,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.975226841898375</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0.1</v>
@@ -373,8 +371,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.30993887734306</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>0.1</v>
@@ -394,8 +391,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.917705283563195</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.1</v>
@@ -415,8 +411,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.649191589278656</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>0.1</v>
@@ -436,8 +431,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.207532443436939</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.1</v>
@@ -457,8 +451,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.624980256183717</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.1</v>
@@ -478,8 +471,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.975329676638525</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>0.1</v>
@@ -499,8 +491,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.653767790478176</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>0.1</v>
@@ -520,8 +511,7 @@
         <v>24</v>
       </c>
       <c r="E11" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.702911625671856</v>
+        <v>1</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>0.1</v>
@@ -541,8 +531,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.130352751211588</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>0.1</v>
@@ -562,8 +551,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.62146025019331</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>0.1</v>
@@ -583,8 +571,7 @@
         <v>26</v>
       </c>
       <c r="E14" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.251647985892237</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>0.1</v>
@@ -604,8 +591,7 @@
         <v>26</v>
       </c>
       <c r="E15" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.427589867002515</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>0.1</v>
@@ -625,8 +611,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.994698002424131</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>0.1</v>
@@ -646,8 +631,7 @@
         <v>26</v>
       </c>
       <c r="E17" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.563930033264676</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0.1</v>
@@ -667,8 +651,7 @@
         <v>26</v>
       </c>
       <c r="E18" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.0658305426995954</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0.1</v>
@@ -688,8 +671,7 @@
         <v>31</v>
       </c>
       <c r="E19" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.585271010368509</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>0.1</v>
@@ -709,8 +691,7 @@
         <v>32</v>
       </c>
       <c r="E20" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.176428802857364</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>0.1</v>
@@ -730,8 +711,7 @@
         <v>32</v>
       </c>
       <c r="E21" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.267785630167501</v>
+        <v>1</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>0.1</v>
@@ -751,8 +731,7 @@
         <v>32</v>
       </c>
       <c r="E22" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.895197364189645</v>
+        <v>1</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>0.1</v>
@@ -772,8 +751,7 @@
         <v>32</v>
       </c>
       <c r="E23" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.215037446114134</v>
+        <v>1</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>0.1</v>
@@ -793,8 +771,7 @@
         <v>34</v>
       </c>
       <c r="E24" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.737851123088268</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>0.1</v>
@@ -814,8 +791,7 @@
         <v>35</v>
       </c>
       <c r="E25" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.516436415646474</v>
+        <v>1</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>0.1</v>
@@ -835,8 +811,7 @@
         <v>36</v>
       </c>
       <c r="E26" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.226250479775035</v>
+        <v>1</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>0.1</v>
@@ -856,8 +831,7 @@
         <v>16</v>
       </c>
       <c r="E27" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.237352695016852</v>
+        <v>1</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>0.1</v>
@@ -877,8 +851,7 @@
         <v>37</v>
       </c>
       <c r="E28" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.666864787859761</v>
+        <v>1</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>0.1</v>
@@ -898,8 +871,7 @@
         <v>37</v>
       </c>
       <c r="E29" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.0202374707868166</v>
+        <v>1</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>0.1</v>
@@ -919,8 +891,7 @@
         <v>38</v>
       </c>
       <c r="E30" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.540601229266589</v>
+        <v>1</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>0.1</v>
@@ -940,8 +911,7 @@
         <v>39</v>
       </c>
       <c r="E31" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.203187480975926</v>
+        <v>1</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>0.1</v>
@@ -961,8 +931,7 @@
         <v>40</v>
       </c>
       <c r="E32" s="4" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.604443658361369</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0.1</v>
@@ -981,8 +950,8 @@
       <c r="D33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>0.8</v>
+      <c r="E33" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>0.1</v>
